--- a/reminders.xlsx
+++ b/reminders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C3C1B1-820B-4B58-ABB9-C621CB090E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D266602E-545D-491D-97A4-C2264508B7D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="740" windowWidth="19180" windowHeight="10060" xr2:uid="{23F0A8AE-A2F0-4A59-8176-3BA8ACE6574B}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{23F0A8AE-A2F0-4A59-8176-3BA8ACE6574B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -514,7 +514,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>14</v>
@@ -531,7 +531,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="3">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>15</v>
@@ -565,7 +565,7 @@
         <v>13</v>
       </c>
       <c r="C5" s="3">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>

--- a/reminders.xlsx
+++ b/reminders.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C3C1B1-820B-4B58-ABB9-C621CB090E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E949C624-838F-42DF-ABCF-15C2224E0FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="740" windowWidth="19180" windowHeight="10060" xr2:uid="{23F0A8AE-A2F0-4A59-8176-3BA8ACE6574B}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{23F0A8AE-A2F0-4A59-8176-3BA8ACE6574B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -514,7 +515,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>14</v>
@@ -531,7 +532,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="3">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>15</v>
@@ -548,7 +549,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="3">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>14</v>
@@ -565,7 +566,7 @@
         <v>13</v>
       </c>
       <c r="C5" s="3">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>

--- a/reminders.xlsx
+++ b/reminders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E949C624-838F-42DF-ABCF-15C2224E0FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD8BE002-D514-42E2-9F82-F03F042A87F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{23F0A8AE-A2F0-4A59-8176-3BA8ACE6574B}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -515,7 +514,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>14</v>
@@ -532,7 +531,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="3">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>15</v>
@@ -549,7 +548,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="3">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>14</v>
@@ -566,7 +565,7 @@
         <v>13</v>
       </c>
       <c r="C5" s="3">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>

--- a/reminders.xlsx
+++ b/reminders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD8BE002-D514-42E2-9F82-F03F042A87F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{121872C4-5C6D-4C0C-9A1B-A0D112FEDEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{23F0A8AE-A2F0-4A59-8176-3BA8ACE6574B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="18">
   <si>
     <t>reminder_text</t>
   </si>
@@ -480,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DFB52D3-F082-46EC-BB93-61B8480EAAF8}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -514,7 +514,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>14</v>
@@ -531,7 +531,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="3">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>15</v>
@@ -548,7 +548,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="3">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>14</v>
@@ -573,6 +573,200 @@
       <c r="E5" s="2" t="s">
         <v>7</v>
       </c>
+    </row>
+    <row r="6" spans="1:5" ht="42" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3">
+        <v>46134</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="56" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="3">
+        <v>46134</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="42" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="3">
+        <v>46134</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="42" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="3">
+        <v>46135</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="42" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="3">
+        <v>46135</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="56" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="3">
+        <v>46135</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="42" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="3">
+        <v>46135</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="42" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="3">
+        <v>46136</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="42" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="3">
+        <v>46136</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="56" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="3">
+        <v>46136</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="42" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="3">
+        <v>46136</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/reminders.xlsx
+++ b/reminders.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{121872C4-5C6D-4C0C-9A1B-A0D112FEDEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B412D2E3-D00E-4C08-928D-8EE87580A2F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{23F0A8AE-A2F0-4A59-8176-3BA8ACE6574B}"/>
+    <workbookView xWindow="20" yWindow="740" windowWidth="19180" windowHeight="10060" xr2:uid="{23F0A8AE-A2F0-4A59-8176-3BA8ACE6574B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -514,7 +514,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3">
-        <v>46133</v>
+        <v>46137</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>14</v>
@@ -531,7 +531,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="3">
-        <v>46133</v>
+        <v>46137</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>15</v>
@@ -548,7 +548,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="3">
-        <v>46133</v>
+        <v>46137</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>14</v>
@@ -565,7 +565,7 @@
         <v>13</v>
       </c>
       <c r="C5" s="3">
-        <v>46133</v>
+        <v>46137</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
@@ -582,7 +582,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="3">
-        <v>46134</v>
+        <v>46138</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>14</v>
@@ -599,7 +599,7 @@
         <v>9</v>
       </c>
       <c r="C7" s="3">
-        <v>46134</v>
+        <v>46138</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>15</v>
@@ -616,7 +616,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="3">
-        <v>46134</v>
+        <v>46138</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>14</v>
@@ -633,7 +633,7 @@
         <v>13</v>
       </c>
       <c r="C9" s="3">
-        <v>46135</v>
+        <v>46138</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>15</v>
@@ -650,7 +650,7 @@
         <v>6</v>
       </c>
       <c r="C10" s="3">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>14</v>
@@ -667,7 +667,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="3">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>15</v>
@@ -684,7 +684,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="3">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>14</v>
@@ -701,7 +701,7 @@
         <v>13</v>
       </c>
       <c r="C13" s="3">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>15</v>
@@ -718,7 +718,7 @@
         <v>6</v>
       </c>
       <c r="C14" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>14</v>
@@ -735,7 +735,7 @@
         <v>9</v>
       </c>
       <c r="C15" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>15</v>
@@ -752,7 +752,7 @@
         <v>11</v>
       </c>
       <c r="C16" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>14</v>

--- a/reminders.xlsx
+++ b/reminders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B412D2E3-D00E-4C08-928D-8EE87580A2F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{778ECE6A-F7F6-42DB-9F1A-ABFD08A8A99D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="740" windowWidth="19180" windowHeight="10060" xr2:uid="{23F0A8AE-A2F0-4A59-8176-3BA8ACE6574B}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{23F0A8AE-A2F0-4A59-8176-3BA8ACE6574B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -514,7 +514,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3">
-        <v>46137</v>
+        <v>46142</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>14</v>
@@ -531,7 +531,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="3">
-        <v>46137</v>
+        <v>46142</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>15</v>
@@ -548,7 +548,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="3">
-        <v>46137</v>
+        <v>46142</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>14</v>
@@ -565,7 +565,7 @@
         <v>13</v>
       </c>
       <c r="C5" s="3">
-        <v>46137</v>
+        <v>46143</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
@@ -582,7 +582,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="3">
-        <v>46138</v>
+        <v>46143</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>14</v>
@@ -599,7 +599,7 @@
         <v>9</v>
       </c>
       <c r="C7" s="3">
-        <v>46138</v>
+        <v>46143</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>15</v>
@@ -616,7 +616,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="3">
-        <v>46138</v>
+        <v>46144</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>14</v>
@@ -633,7 +633,7 @@
         <v>13</v>
       </c>
       <c r="C9" s="3">
-        <v>46138</v>
+        <v>46144</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>15</v>
@@ -650,7 +650,7 @@
         <v>6</v>
       </c>
       <c r="C10" s="3">
-        <v>46139</v>
+        <v>46144</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>14</v>
@@ -667,7 +667,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="3">
-        <v>46139</v>
+        <v>46145</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>15</v>
@@ -684,7 +684,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="3">
-        <v>46139</v>
+        <v>46145</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>14</v>
@@ -701,7 +701,7 @@
         <v>13</v>
       </c>
       <c r="C13" s="3">
-        <v>46139</v>
+        <v>46145</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>15</v>
@@ -718,7 +718,7 @@
         <v>6</v>
       </c>
       <c r="C14" s="3">
-        <v>46140</v>
+        <v>46146</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>14</v>
@@ -735,7 +735,7 @@
         <v>9</v>
       </c>
       <c r="C15" s="3">
-        <v>46140</v>
+        <v>46146</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>15</v>
@@ -752,7 +752,7 @@
         <v>11</v>
       </c>
       <c r="C16" s="3">
-        <v>46140</v>
+        <v>46146</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>14</v>

--- a/reminders.xlsx
+++ b/reminders.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{778ECE6A-F7F6-42DB-9F1A-ABFD08A8A99D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{075AFF6F-84C8-4940-A688-5E5AC79C8BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{23F0A8AE-A2F0-4A59-8176-3BA8ACE6574B}"/>
   </bookViews>
@@ -514,7 +514,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>14</v>
@@ -531,7 +531,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>15</v>
@@ -548,7 +548,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>14</v>
@@ -565,7 +565,7 @@
         <v>13</v>
       </c>
       <c r="C5" s="3">
-        <v>46143</v>
+        <v>46149</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
@@ -582,7 +582,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="3">
-        <v>46143</v>
+        <v>46149</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>14</v>
@@ -599,7 +599,7 @@
         <v>9</v>
       </c>
       <c r="C7" s="3">
-        <v>46143</v>
+        <v>46149</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>15</v>
@@ -616,7 +616,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="3">
-        <v>46144</v>
+        <v>46150</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>14</v>
@@ -633,7 +633,7 @@
         <v>13</v>
       </c>
       <c r="C9" s="3">
-        <v>46144</v>
+        <v>46150</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>15</v>
@@ -650,7 +650,7 @@
         <v>6</v>
       </c>
       <c r="C10" s="3">
-        <v>46144</v>
+        <v>46150</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>14</v>
@@ -667,7 +667,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="3">
-        <v>46145</v>
+        <v>46151</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>15</v>
@@ -684,7 +684,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="3">
-        <v>46145</v>
+        <v>46151</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>14</v>
@@ -701,7 +701,7 @@
         <v>13</v>
       </c>
       <c r="C13" s="3">
-        <v>46145</v>
+        <v>46151</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>15</v>
@@ -718,7 +718,7 @@
         <v>6</v>
       </c>
       <c r="C14" s="3">
-        <v>46146</v>
+        <v>46152</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>14</v>
@@ -735,7 +735,7 @@
         <v>9</v>
       </c>
       <c r="C15" s="3">
-        <v>46146</v>
+        <v>46152</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>15</v>
@@ -752,7 +752,7 @@
         <v>11</v>
       </c>
       <c r="C16" s="3">
-        <v>46146</v>
+        <v>46152</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>14</v>
